--- a/data_extactor/batch_10_fa/batch_0047_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0047_fa.xlsx
@@ -498,37 +498,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MD (Medical Doctor) | Medical Director Acute Rehabilitation Unit Physiatrist | Pain Management Physician | Pediatric Physiatrist | Physiatrist | Physical Medicine and Rehabilitation Physician (PM and R Physician) | Physician | Rehabilitation Physician</t>
+          <t>MD (دکترای پزشکی) | متخصص طب فیزیکی و مدیر پزشکی بخش توان‌بخشی حاد | پزشک مدیریت درد | متخصص طب فیزیکی کودکان | متخصص طب فیزیکی و توان‌بخشی | پزشک طب فیزیکی و توان‌بخشی (PM and R) | پزشک | پزشک توان‌بخشی</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Biodex Medical Systems Biodex Concussion Manager | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | Nuesoft Technologies NueMD | OmniMD PT./OT EHR | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | eClinicalWorks EHR software | simplifyMD</t>
+          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Biodex Medical Systems Biodex Concussion Manager | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | Nuesoft Technologies NueMD | OmniMD PT./OT EHR | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | نرم‌افزار eClinicalWorks EHR | simplifyMD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخنوری | گوش دادن فعال | درک مطلب | نظارت | نوشتن | یادگیری فعال | علوم | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | روانشناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | جامعه‌شناسی و مردم‌شناسی | حقوق و دولت | شیمی | کامپیوتر و الکترونیک | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت | شیمی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک نوشتاری | بیان نوشتاری | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید نزدیک | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | خلاقیت | انعطاف‌پذیری بستار | تجسم | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | تجسم | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | نزدیکی فیزیکی | تماس با دیگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | در معرض بیماری یا عفونت | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | تکرار تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | نتایج کاری و خروجی‌های سایر کارکنان | فشار زمانی | سلامت و ایمنی سایر کارکنان | سطح رقابت</t>
+          <t>آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | سلامت و ایمنی سایر کارکنان | سطح رقابت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Advanced Practice Psychiatric Nurses | Anesthesiologists | Cardiologists | Chiropractors | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Neurologists | Nurse Practitioners | Occupational Therapists | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Therapist Assistants | Physical Therapists | Physician Assistants | Psychiatric Technicians | Psychiatrists | Urologists</t>
+          <t>پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران متخصص | کاردرمانگران | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | دستیاران پزشک | تکنسین‌های روانپزشکی | روان‌پزشکان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Occupational Medicine Physician | Occupational Physician | Physician | Preventive Medicine Physician | Primary Clinician | Public Health Officer | Public Health Physician</t>
+          <t>پزشک طب کار | پزشک طب کار | پزشک | پزشک طب پیشگیری | درمانگر اصلی | مسئول بهداشت عمومی | پزشک بهداشت عمومی</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | نوشتن | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | روانشناسی | حقوق و دولت | مدیریت و اداره | درمان و مشاوره | ریاضیات | پرسنل و منابع انسانی | خدمات مشتری و شخصی | کامپیوتر و الکترونیک | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | روان‌شناسی | قانون و دولت | مدیریت و اداره | درمان و مشاوره | ریاضیات | پرسنل و منابع انسانی | خدمات مشتری و شخصی | رایانه و الکترونیک | شیمی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک نوشتاری | حساسیت به مسئله | وضوح گفتار | بیان نوشتاری | روانی ایده‌ها | تشخیص گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید نزدیک | انعطاف‌پذیری بستار | خلاقیت | توجه انتخابی | استدلال ریاضی | توانایی عددی | تجسم | سرعت بستار | حافظه‌سپاری | سرعت ادراکی</t>
+          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | وضوح گفتار | بیان کتبی | روانی ایده‌ها | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | انعطاف‌پذیری بستار | اصالت | توجه انتخابی | استدلال ریاضی | توانایی عددی | تجسم | سرعت بستار | حفظ کردن | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | تماس با دیگران | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | نتایج کاری و خروجی‌های سایر کارکنان | پیامد خطا | سطح رقابت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان | پیامد خطا | سطح رقابت</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Allergists and Immunologists | Cardiologists | Clinical Nurse Specialists | Emergency Medicine Physicians | Epidemiologists | Family Medicine Physicians | General Internal Medicine Physicians | Naturopathic Physicians | Neurologists | Nurse Practitioners | Obstetricians and Gynecologists | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Psychiatric Technicians | Psychiatrists | Registered Nurses</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان آلرژی و ایمونولوژی | متخصصان قلب | متخصصان پرستاری بالینی | پزشکان طب اورژانس | اپیدمیولوژیست‌ها | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | تکنسین‌های روانپزشکی | روان‌پزشکان | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,37 +612,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Athletic Team Physician | Nonsurgical Primary Care Sports Medicine Physician | Orthopedic Team Physician | Physician | Sports Medicine Physician | Team Physician</t>
+          <t>پزشک تیم ورزشی | پزشک طب ورزشی مراقبت اولیه غیرجراحی | پزشک ارتوپدی تیم ورزشی | پزشک | پزشک طب ورزشی | پزشک تیم</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار تحلیل حرکت سه‌بعدی | Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Meditab IMS Orthopedics/Sports Medicine | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | OmniMD Sports Medicine EHR | PracticeSuite Complete Suite | Presagia Sports | SpartaTrac | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | نرم‌افزار مرورگر وب | athenahealth athenaCollector | eClinicalWorks EHR software | simplifyMD</t>
+          <t>نرم‌افزار تحلیل حرکت سه‌بعدی | Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Meditab IMS Orthopedics/Sports Medicine | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | OmniMD Sports Medicine EHR | PracticeSuite Complete Suite | Presagia Sports | SpartaTrac | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | نرم‌افزار مرورگر وب | athenahealth athenaCollector | نرم‌افزار eClinicalWorks EHR | simplifyMD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخنوری | یادگیری فعال | نوشتن | راهبردهای یادگیری | علوم</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | آموزش و پرورش</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک نوشتاری | بیان شفاهی | استدلال استقرایی | بیان نوشتاری | استدلال قیاسی | وضوح گفتار | دید نزدیک | تشخیص گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | خلاقیت | روانی ایده‌ها | تجسم | توجه انتخابی | ثبات دست و بازو | مهارت انگشتان | سرعت ادراکی | دید دور | سرعت بستار</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | بیان کتبی | استدلال قیاسی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | تجسم | توجه انتخابی | ثبات دست و بازو | مهارت انگشتان | سرعت ادراکی | بینایی دور | سرعت بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | تکرار تصمیم‌گیری | تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض بیماری یا عفونت | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | پیامد خطا | نتایج کاری و خروجی‌های سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دستان جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | سطح رقابت | موقعیت‌های تعارض</t>
+          <t>اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | سطح رقابت | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Anesthesiologists | Athletic Trainers | Cardiologists | Chiropractors | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Naturopathic Physicians | Neurologists | Nurse Practitioners | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physical Therapists | Podiatrists | Urologists</t>
+          <t>متخصصان بیهوشی | مربیان ورزشی | متخصصان قلب | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | پزشکان پا | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -669,37 +669,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clinical Ophthalmologist | Cornea Specialist | Glaucoma Specialist | Oculoplastic Specialist | Ophthalmic Surgeon | Ophthalmologist | Ophthalmologist Specialist | Physician | Retina Specialist | Surgical Ophthalmologist</t>
+          <t>چشم‌پزشک بالینی | متخصص قرنیه | متخصص آب سیاه چشم | متخصص جراحی پلاستیک چشم | جراح چشم | چشم‌پزشک | متخصص چشم‌پزشکی | پزشک | متخصص شبکیه | چشم‌پزشک جراح</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | EyeMD EMR Healthcare Systems EyeMD EMR | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Microsoft Excel | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | نرم‌افزار تصویربرداری چشمی | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | eClinicalWorks EHR software | simplifyMD</t>
+          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | EyeMD EMR Healthcare Systems EyeMD EMR | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Microsoft Excel | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | نرم‌افزار تصویربرداری چشمی | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | نرم‌افزار eClinicalWorks EHR | simplifyMD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخنوری | نوشتن | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | خدمات مشتری و شخصی | زیست‌شناسی | مدیریت و اداره | آموزش و پرورش | ریاضیات | کامپیوتر و الکترونیک | روانشناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | خدمات مشتری و شخصی | زیست‌شناسی | مدیریت و اداره | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | روان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک نوشتاری | دید نزدیک | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | درک شفاهی | بیان نوشتاری | تشخیص گفتار | وضوح گفتار | مهارت انگشتان | انعطاف‌پذیری بستار | نظم‌دهی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | دقت کنترل | سرعت ادراکی | خلاقیت | دید دور | مهارت دستی | تشخیص رنگ بصری | استدلال ریاضی | روانی ایده‌ها | تجسم | توانایی عددی</t>
+          <t>حساسیت به مسئله | درک کتبی | بینایی نزدیک | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | درک شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | مهارت انگشتان | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | دقت کنترل | سرعت ادراکی | اصالت | بینایی دور | مهارت دستی | تشخیص رنگ بصری | استدلال ریاضی | روانی ایده‌ها | تجسم | توانایی عددی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | تکرار تصمیم‌گیری | تماس با دیگران | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | پیامد خطا | در معرض بیماری یا عفونت | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دستان جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | نتایج کاری و خروجی‌های سایر کارکنان | اهمیت تکرار کارهای مشابه | صرف زمان برای نشستن | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | موقعیت‌های تعارض</t>
+          <t>آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | ارتباط با دیگران | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | پیامد خطا | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان | صرف زمان برای نشستن | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Anesthesiologists | Cardiologists | Chiropractors | Dermatologists | Emergency Medicine Physicians | General Internal Medicine Physicians | Neurologists | Nurse Practitioners | Obstetricians and Gynecologists | Ophthalmic Medical Technicians | Ophthalmic Medical Technologists | Optometrists | Oral and Maxillofacial Surgeons | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Podiatrists | Urologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | اپتومتریست‌ها | جراحان دهان و فک و صورت | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | پزشکان پا | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>General Surgeon | Hand Surgeon | Orthopaedic Surgeon | Orthopedic Surgeon | Physician | Surgeon</t>
+          <t>جراح عمومی | جراح دست | جراح ارتوپدی | جراح ارتوپدی | پزشک | جراح</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | علوم | نظارت | یادگیری فعال | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | روانشناسی | آموزش و پرورش | مدیریت و اداره | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | اشتراک زمانی | دقت کنترل | درک عمق | هماهنگی چند اندامی | قدرت ایستا</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق | هماهنگی چند عضو | قدرت ایستا</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت | نزدیکی فیزیکی | تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | تکرار تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | در معرض تابش | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل، یا حفاظت در برابر تابش</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تابش | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Anesthesiologist Assistants | Anesthesiologists | Cardiologists | Chiropractors | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Medical Assistants | Neurologists | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Oral and Maxillofacial Surgeons | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Podiatrists | Radiologists | Urologists</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | دستیاران پزشکی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان دهان و فک و صورت | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان پا | رادیولوژیست‌ها | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cardiovascular Surgeon | General Surgeon | Hand Surgeon | Physician | Plastic Surgeon | Surgeon | Thoracic Surgeon | Vascular Surgeon</t>
+          <t>جراح قلب و عروق | جراح عمومی | جراح دست | پزشک | جراح پلاستیک | جراح | جراح قفسه سینه | جراح عروق</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | علوم | نظارت | یادگیری فعال | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | روانشناسی | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | درمان و مشاوره | آموزش و پرورش | مدیریت و اداره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | درمان و مشاوره | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | اشتراک زمانی | دقت کنترل | درک عمق | هماهنگی چند اندامی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت | نزدیکی فیزیکی | تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | تکرار تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | در معرض تابش | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل، یا حفاظت در برابر تابش</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تابش | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Anesthesiologist Assistants | Anesthesiologists | Cardiologists | Chiropractors | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Medical Assistants | Neurologists | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Oral and Maxillofacial Surgeons | Orthopedic Surgeons, Except Pediatric | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Radiologists | Urologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | دستیاران پزشکی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان دهان و فک و صورت | جراحان ارتوپد، به‌جز کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | رادیولوژیست‌ها | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cardiothoracic Surgeon | Colorectal Surgeon | General Surgeon | Neurological Surgeon | Plastic Surgeon | Surgeon | Thoracic Surgeon | Transplant Surgeon | Trauma Surgeon | Vascular Surgeon</t>
+          <t>جراح قلب و قفسه سینه | جراح روده بزرگ و مقعد | جراح عمومی | جراح مغز و اعصاب | جراح پلاستیک | جراح | جراح قفسه سینه | جراح پیوند اعضا | جراح تروما | جراح عروق</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | علوم | نظارت | یادگیری فعال | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | روانشناسی | آموزش و پرورش | مدیریت و اداره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | اشتراک زمانی | دقت کنترل | درک عمق | هماهنگی چند اندامی | زمان واکنش</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق | هماهنگی چند عضو | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت | نزدیکی فیزیکی | تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | تکرار تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | در معرض تابش | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل، یا حفاظت در برابر تابش</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تابش | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Ophthalmologists, Except Pediatric | Oral and Maxillofacial Surgeons | Urologists | Anesthesiologists | Emergency Medicine Physicians | Physicians, All Other | General Internal Medicine Physicians | Cardiologists | Neurologists | Physicians, Pathologists | Radiologists | Physician Assistants | Surgical Assistants | Surgical Technologists | Registered Nurses | Nurse Anesthetists | Health Specialties Teachers, Postsecondary | Medical and Health Services Managers</t>
+          <t>جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | چشم‌پزشکان، به‌جز کودکان | جراحان دهان و فک و صورت | اورولوژیست‌ها | متخصصان بیهوشی | پزشکان طب اورژانس | پزشکان، سایر موارد | پزشکان داخلی عمومی | متخصصان قلب | متخصصان مغز و اعصاب | پزشکان، آسیب‌شناسان | رادیولوژیست‌ها | دستیاران پزشک | دستیاران جراحی | تکنولوژیست‌های جراحی | پرستاران ثبت‌شده | پرستاران بیهوشی | استادان تخصص‌های بهداشتی، پس از متوسطه | مدیران خدمات پزشکی و بهداشتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Acupuncture Doctor | Acupuncture Physician | Acupuncture Provider | Acupuncturist | Chinese Medical Doctor (Chinese MD) | Chinese Medicine Doctor | Herbalist | Licensed Acupuncturist (LAC) | Oriental Medicine Provider | Traditional Chinese Medicine Doctor</t>
+          <t>پزشک طب سوزنی | پزشک طب سوزنی | ارائه‌دهنده خدمات طب سوزنی | متخصص طب سوزنی | پزشک طب چینی (Chinese MD) | پزشک طب چینی | گیاه‌درمانگر | متخصص طب سوزنی دارای پروانه (LAC) | ارائه‌دهنده خدمات طب شرقی | پزشک طب سنتی چینی</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | سخنوری | نظارت | درک مطلب | نوشتن | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | پزشکی و دندانپزشکی | روانشناسی | زیست‌شناسی | زبان انگلیسی | اداری | درمان و مشاوره | مدیریت و اداره | آموزش و پرورش | فروش و بازاریابی | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | روان‌شناسی | زیست‌شناسی | زبان انگلیسی | اداری | درمان و مشاوره | مدیریت و اداره | آموزش و پرورش | فروش و بازاریابی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک نوشتاری | استدلال استقرایی | ثبات دست و بازو | مهارت انگشتان | وضوح گفتار | بیان نوشتاری | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | استدلال استقرایی | ثبات دست و بازو | مهارت انگشتان | وضوح گفتار | بیان کتبی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>نزدیکی فیزیکی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های رودررو با افراد و درون تیم‌ها | ایمیل | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | صرف زمان برای استفاده از دستان جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | در معرض بیماری یا عفونت | اهمیت دقیق یا صحیح بودن | تکرار تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>نزدیکی فیزیکی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Cardiologists | Chiropractors | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Massage Therapists | Naturopathic Physicians | Neurologists | Nurse Practitioners | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physical Therapists | Psychiatrists | Urologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان قلب | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | ماساژدرمانگران | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | روان‌پزشکان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dental Hygienist | Hygienist | Licensed Dental Hygienist | Pediatric Dental Hygienist | Registered Dental Hygienist (RDH)</t>
+          <t>بهداشت‌کار دهان و دندان | بهداشت‌کار | بهداشت‌کار دهان و دندان دارای پروانه | بهداشت‌کار دهان و دندان کودکان | بهداشت‌کار ثبت‌شده دهان و دندان (RDH)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | سخنوری | نوشتن | نظارت | یادگیری فعال | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتری و شخصی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | مهارت انگشتان | دید نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | مهارت دستی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | درک نوشتاری | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | تشخیص رنگ بصری | دقت کنترل | اشتراک زمانی | نظم‌دهی اطلاعات | استدلال قیاسی | بیان نوشتاری</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | مهارت دستی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | درک کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | تشخیص رنگ بصری | دقت کنترل | تقسیم توجه | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دستان جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل محیطی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | در معرض بیماری یا عفونت | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | نزدیکی فیزیکی | اهمیت دقیق یا صحیح بودن | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار کارهای مشابه | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | در معرض تابش | صرف زمان برای خم شدن یا چرخاندن بدن | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی</t>
+          <t>صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | قرار گرفتن در معرض تابش | صرف زمان برای خم کردن یا چرخاندن بدن | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Anesthesiologist Assistants | Anesthesiologists | Dental Assistants | Dentists, General | Dermatologists | Emergency Medicine Physicians | Licensed Practical and Licensed Vocational Nurses | Medical Assistants | Nurse Anesthetists | Nurse Practitioners | Ophthalmic Medical Technicians | Oral and Maxillofacial Surgeons | Orthodontists | Prosthodontists | Registered Nurses | Respiratory Therapists | Surgical Assistants | Surgical Technologists | Veterinary Technologists and Technicians</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان بیهوشی | دستیاران دندان‌پزشکی | دندانپزشکان، عمومی | متخصصان پوست | پزشکان طب اورژانس | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | پرستاران متخصص | تکنسین‌های پزشکی چشم‌پزشکی | جراحان دهان و فک و صورت | متخصصان ارتودنسی | متخصصان پروتز دندان | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Clinical Practitioner | Health Practitioner | Homeopathic Practitioner | Hyperbaric Medicine Practitioner | Massage Therapy Practitioner | Naprapath | Nutrition Practitioner | Sleep Medicine Practitioner | Traditional Medicine Practitioner | Wellness Practitioner</t>
+          <t>درمانگر بالینی | پزشک عمومی | درمانگر هومیوپاتی | درمانگر طب هایپرباریک | درمانگر ماساژ | درمانگر ناپراپاتی | درمانگر تغذیه | درمانگر طب خواب | درمانگر طب سنتی | درمانگر سلامتی</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | علوم | نظارت | یادگیری فعال | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | روانشناسی | زبان انگلیسی | شیمی | آموزش و پرورش</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | روان‌شناسی | زبان انگلیسی | شیمی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | اشتراک زمانی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت | نزدیکی فیزیکی | تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | تکرار تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Acupuncturists | Naturopathic Physicians | Orthoptists | Chiropractors | Dietitians and Nutritionists | Optometrists | Podiatrists | Physician Assistants | Nurse Practitioners | Registered Nurses | Physicians, All Other | Therapists, All Other | Occupational Therapists | Physical Therapists | Exercise Physiologists | Athletic Trainers | Genetic Counselors | Health Education Specialists | Healthcare Practitioners and Technical Workers, All Other | Health Specialties Teachers, Postsecondary</t>
+          <t>طب‌سوزنی‌ها | پزشکان ناتوروپاتی | ارتوپتیست‌ها | کایروپراکتورها | متخصصان رژیم غذایی و تغذیه | اپتومتریست‌ها | پزشکان پا | دستیاران پزشک | پرستاران متخصص | پرستاران ثبت‌شده | پزشکان، سایر موارد | درمانگران، همه موارد دیگر | کاردرمانگران | فیزیوتراپیست‌ها | فیزیولوژیست‌های ورزشی | مربیان ورزشی | مشاوران ژنتیک | متخصصان آموزش بهداشت | پزشکان و کارکنان فنی حوزه سلامت، سایر موارد | استادان تخصص‌های بهداشتی، پس از متوسطه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0047_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0047_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم پایه | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | روانشناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور اداری و منابع انسانی | جامعه‌شناسی و مردم‌شناسی | حقوق و مقررات دولتی | شیمی | رایانه و الکترونیک | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت | شیمی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | دید نزدیک | تشخیص گفتار | وضوح گفتار | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | انعطاف‌پذیری شناختی | تجسم فضایی | توجه انتخابی | سرعت ادراک | سرعت درک الگو</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | تجسم | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران بالینی تخصصی روان‌پزشکی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | متخصصان کایروپراکتیک | متخصصان طب اورژانس | پزشکان عمومی و طب خانواده | متخصصان بیماری‌های داخلی | متخصصان مغز و اعصاب (نورولوژی) | پرستاران پیگیر و بالینی تخصصی | کاردرمانگران | متخصصان چشم‌پزشکی (بزرگسالان) | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص اطفال | کاردان‌های فیزیوتراپی | فیزیوتراپ‌ها | دستیاران پزشک | تکنسین‌های روان‌پزشکی | روان‌پزشکان | متخصصان کلیه و مجاری ادراری (اورولوژیست‌ها)</t>
+          <t>پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | کاردرمانگران | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | دستیاران پزشک | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم پایه | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | روانشناسی | حقوق و مقررات دولتی | مدیریت و امور اداری | درمان و مشاوره | ریاضیات | امور اداری و منابع انسانی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | روان‌شناسی | قانون و دولت | مدیریت و اداره | درمان و مشاوره | ریاضیات | پرسنل و منابع انسانی | خدمات مشتری و شخصی | رایانه و الکترونیک | شیمی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | وضوح گفتار | بیان کتبی | روانی کلام و سیالی ایده‌ها | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | دید نزدیک | انعطاف‌پذیری شناختی | ابتکار و اصالت | توجه انتخابی | استدلال ریاضی | محاسبات عددی | تجسم فضایی | سرعت درک الگو | حافظه و به‌خاطرسپاری | سرعت ادراک</t>
+          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | وضوح گفتار | بیان کتبی | روانی ایده‌ها | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | انعطاف‌پذیری بستار | اصالت | توجه انتخابی | استدلال ریاضی | توانایی عددی | تجسم | سرعت بستار | حفظ کردن | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران بالینی تخصصی روان‌پزشکی | متخصصان آلرژی و ایمونولوژی | متخصصان بیماری‌های قلب و عروق | پرستاران بالینی متخصص | متخصصان طب اورژانس | اپیدمیولوژیست‌ها | پزشکان عمومی و طب خانواده | متخصصان بیماری‌های داخلی | پزشکان طب سنتی و مکمل | متخصصان مغز و اعصاب (نورولوژی) | پرستاران پیگیر و بالینی تخصصی | متخصصان زنان و زایمان | جراحان اطفال | پزشکان متخصص اطفال | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | تکنسین‌های روان‌پزشکی | روان‌پزشکان | پرستاران دارای پروانه</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پزشکان طب اورژانس | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم پایه</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | آموزش و پرورش</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | بیان کتبی | استدلال قیاسی | وضوح گفتار | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری شناختی | انعطاف‌پذیری در دسته‌بندی | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | تجسم فضایی | توجه انتخابی | ثبات دست و بازو | چابکی انگشتان | سرعت ادراک | دید دور | سرعت درک الگو</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | بیان کتبی | استدلال قیاسی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | تجسم | توجه انتخابی | ثبات دست و بازو | مهارت انگشتان | سرعت ادراکی | بینایی دور | سرعت بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | مربیان بدنساز و مربیان توانبخشی ورزشی | متخصصان بیماری‌های قلب و عروق | متخصصان کایروپراکتیک | متخصصان پوست و مو | متخصصان طب اورژانس | پزشکان عمومی و طب خانواده | متخصصان بیماری‌های داخلی | پزشکان طب سنتی و مکمل | متخصصان مغز و اعصاب (نورولوژی) | پرستاران پیگیر و بالینی تخصصی | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی (بزرگسالان) | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص اطفال | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپ‌ها | متخصصان بیماری‌های پا (پودیاتریست‌ها) | متخصصان کلیه و مجاری ادراری (اورولوژیست‌ها)</t>
+          <t>متخصصان بیهوشی | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | پزشکان متخصص پا و مچ پا | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم پایه | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | مدیریت و امور اداری | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | روانشناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | خدمات مشتری و شخصی | زیست‌شناسی | مدیریت و اداره | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | روان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک کتبی | دید نزدیک | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | درک شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | چابکی انگشتان | انعطاف‌پذیری شناختی | مرتب‌سازی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری در دسته‌بندی | توجه انتخابی | دقت کنترل ابزار و حرکات | سرعت ادراک | ابتکار و اصالت | دید دور | چابکی دستی | تشخیص رنگ‌ها | استدلال ریاضی | روانی کلام و سیالی ایده‌ها | تجسم فضایی | محاسبات عددی</t>
+          <t>حساسیت به مسئله | درک کتبی | بینایی نزدیک | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | درک شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | مهارت انگشتان | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | دقت کنترل | سرعت ادراکی | اصالت | بینایی دور | مهارت دستی | تشخیص رنگ بصری | استدلال ریاضی | روانی ایده‌ها | تجسم | توانایی عددی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | متخصصان کایروپراکتیک | متخصصان پوست و مو | متخصصان طب اورژانس | متخصصان بیماری‌های داخلی | متخصصان مغز و اعصاب (نورولوژی) | پرستاران پیگیر و بالینی تخصصی | متخصصان زنان و زایمان | تکنسین‌های معاینات چشم‌پزشکی | تکنسین‌های ارشد اپتومتری و چشم‌شناسی | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص اطفال | متخصصان طب فیزیکی و توانبخشی | متخصصان بیماری‌های پا (پودیاتریست‌ها) | متخصصان کلیه و مجاری ادراری (اورولوژیست‌ها)</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پا و مچ پا | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | شیمی | روانشناسی | آموزش و پرورش | مدیریت و امور اداری | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | تجسم فضایی | اشتراک زمان و توجه همزمان | دقت کنترل ابزار و حرکات | درک عمق | هماهنگی اندام‌های حرکتی | قدرت بدنی ایستا</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق | هماهنگی چند عضو | قدرت ایستا</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | متخصصان کایروپراکتیک | متخصصان پوست و مو | متخصصان طب اورژانس | پزشکان عمومی و طب خانواده | متخصصان بیماری‌های داخلی | کمک‌پزشکان و دستیاران بالینی | متخصصان مغز و اعصاب (نورولوژی) | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی (بزرگسالان) | جراحان دهان، فک و صورت | جراحان اطفال | پزشکان متخصص اطفال | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان بیماری‌های پا (پودیاتریست‌ها) | متخصصان رادیولوژی | متخصصان کلیه و مجاری ادراری (اورولوژیست‌ها)</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | کمک‌پزشکان و دستیاران مطب | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان دهان، فک و صورت | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان متخصص پا و مچ پا | متخصصان رادیولوژی | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | روانشناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | شیمی | درمان و مشاوره | آموزش و پرورش | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | درمان و مشاوره | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | تجسم فضایی | اشتراک زمان و توجه همزمان | دقت کنترل ابزار و حرکات | درک عمق | هماهنگی اندام‌های حرکتی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | متخصصان کایروپراکتیک | متخصصان پوست و مو | متخصصان طب اورژانس | پزشکان عمومی و طب خانواده | متخصصان بیماری‌های داخلی | کمک‌پزشکان و دستیاران بالینی | متخصصان مغز و اعصاب (نورولوژی) | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی (بزرگسالان) | جراحان دهان، فک و صورت | جراحان ارتوپدی (بزرگسالان) | پزشکان متخصص اطفال | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان رادیولوژی | متخصصان کلیه و مجاری ادراری (اورولوژیست‌ها)</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | کمک‌پزشکان و دستیاران مطب | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان دهان، فک و صورت | جراحان ارتوپدی، غیر از اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان رادیولوژی | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | روانشناسی | آموزش و پرورش | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | تجسم فضایی | اشتراک زمان و توجه همزمان | دقت کنترل ابزار و حرکات | درک عمق | هماهنگی اندام‌های حرکتی | زمان واکنش</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق | هماهنگی چند عضو | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | متخصصان چشم‌پزشکی (بزرگسالان) | جراحان دهان، فک و صورت | متخصصان کلیه و مجاری ادراری (اورولوژیست‌ها) | متخصصان بیهوشی | متخصصان طب اورژانس | سایر پزشکان متخصص | متخصصان بیماری‌های داخلی | متخصصان بیماری‌های قلب و عروق | متخصصان مغز و اعصاب (نورولوژی) | متخصصان آسیب‌شناسی (پاتولوژیست‌ها) | متخصصان رادیولوژی | دستیاران پزشک | دستیاران جراحی | تکنسین‌های اتاق عمل | پرستاران دارای پروانه | پرستاران بیهوشی | اساتید علوم پزشکی و پیراپزشکی در دانشگاه‌ها | مدیران خدمات درمانی و بهداشتی</t>
+          <t>جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان دهان، فک و صورت | متخصصان اورولوژی | متخصصان بیهوشی | پزشکان طب اورژانس | پزشکان، سایر تخصص‌ها | پزشکان متخصص بیماری‌های داخلی | متخصصان بیماری‌های قلب و عروق | متخصصان مغز و اعصاب | پزشکان متخصص پاتولوژی | متخصصان رادیولوژی | دستیاران پزشک | دستیاران جراحی | تکنسین‌های اتاق عمل | پرستاران | پرستاران بیهوشی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | مدیران خدمات درمانی و بهداشتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | نظارت | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | روانشناسی | زیست‌شناسی | زبان انگلیسی | امور اداری و دفتری | درمان و مشاوره | مدیریت و امور اداری | آموزش و پرورش | بازاریابی و فروش | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | روان‌شناسی | زیست‌شناسی | زبان انگلیسی | اداری | درمان و مشاوره | مدیریت و اداره | آموزش و پرورش | فروش و بازاریابی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | استدلال استقرایی | ثبات دست و بازو | چابکی انگشتان | وضوح گفتار | بیان کتبی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری شناختی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | استدلال استقرایی | ثبات دست و بازو | مهارت انگشتان | وضوح گفتار | بیان کتبی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیماری‌های قلب و عروق | متخصصان کایروپراکتیک | متخصصان پوست و مو | متخصصان طب اورژانس | پزشکان عمومی و طب خانواده | متخصصان بیماری‌های داخلی | ماساژدرمانگران | پزشکان طب سنتی و مکمل | متخصصان مغز و اعصاب (نورولوژی) | پرستاران پیگیر و بالینی تخصصی | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی (بزرگسالان) | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص اطفال | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپ‌ها | روان‌پزشکان | متخصصان کلیه و مجاری ادراری (اورولوژیست‌ها)</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | ماساژدرمانگران | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | روان‌پزشکان | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | دید نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | چابکی دستی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | درک کتبی | انعطاف‌پذیری در دسته‌بندی | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری شناختی | تشخیص رنگ‌ها | دقت کنترل ابزار و حرکات | اشتراک زمان و توجه همزمان | مرتب‌سازی اطلاعات | استدلال قیاسی | بیان کتبی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | مهارت دستی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | درک کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | تشخیص رنگ بصری | دقت کنترل | تقسیم توجه | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان بیهوشی | دستیاران دندانپزشک | دندانپزشکان عمومی | متخصصان پوست و مو | متخصصان طب اورژانس | بهیاران و کمک‌پرستاران دارای پروانه | کمک‌پزشکان و دستیاران بالینی | پرستاران بیهوشی | پرستاران پیگیر و بالینی تخصصی | تکنسین‌های معاینات چشم‌پزشکی | جراحان دهان، فک و صورت | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | پرستاران دارای پروانه | متخصصان درمان‌های تنفسی | دستیاران جراحی | تکنسین‌های اتاق عمل | کارشناسان و تکنسین‌های دامپزشکی</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | دستیاران دندان‌پزشک | دندان‌پزشکان عمومی | متخصصان پوست و مو | پزشکان طب اورژانس | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | پرستاران بیهوشی | پرستاران بالینی پیشرفته | تکنسین‌های مراقبت‌های چشمی | جراحان دهان، فک و صورت | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | روانشناسی | زبان انگلیسی | شیمی | آموزش و پرورش</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | روان‌شناسی | زبان انگلیسی | شیمی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | تجسم فضایی | اشتراک زمان و توجه همزمان</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان و کارشناسان طب سوزنی | پزشکان طب سنتی و مکمل | ارتوپتیست‌ها | متخصصان کایروپراکتیک | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | بینایی‌سنج‌ها (اپتومتریست‌ها) | متخصصان بیماری‌های پا (پودیاتریست‌ها) | دستیاران پزشک | پرستاران پیگیر و بالینی تخصصی | پرستاران دارای پروانه | سایر پزشکان متخصص | سایر متخصصان درمان و توانبخشی | کاردرمانگران | فیزیوتراپ‌ها | فیزیولوژیست‌های ورزشی | مربیان بدنساز و مربیان توانبخشی ورزشی | مشاوران ژنتیک | کارشناسان آموزش و ارتقای سلامت | سایر متخصصان و کارشناسان حوزه سلامت | اساتید علوم پزشکی و پیراپزشکی در دانشگاه‌ها</t>
+          <t>متخصصان و کارشناسان طب سوزنی | پزشکان طب طبیعی و نتوپاتی | ارتوپتیست‌ها / متخصصان ارتوپتیک | کایروپراکتورها / متخصصان درمان دستی | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | بینایی‌سنج‌ها (اپتومتریست‌ها) | پزشکان متخصص پا و مچ پا | دستیاران پزشک | پرستاران بالینی پیشرفته | پرستاران | پزشکان، سایر تخصص‌ها | سایر درمانگران | کاردرمانگران | فیزیوتراپیست‌ها | فیزیولوژیست‌های ورزشی | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | مشاوران ژنتیک | کارشناسان آموزش بهداشت و ارتقای سلامت | سایر کارشناسان و متخصصان حوزه سلامت و بهداشت | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
